--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.60078743726724</v>
+        <v>2.697627958555926</v>
       </c>
       <c r="D2" t="n">
-        <v>17.18145070556908</v>
+        <v>2.791985739654975</v>
       </c>
       <c r="E2" t="n">
-        <v>9.721131940903236</v>
+        <v>1.579683940396776</v>
       </c>
       <c r="F2" t="n">
-        <v>9.692963494232188</v>
+        <v>1.575106567812731</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.56670116621797</v>
+        <v>1.717088939510421</v>
       </c>
       <c r="D3" t="n">
-        <v>10.60731355501511</v>
+        <v>1.723688452689955</v>
       </c>
       <c r="E3" t="n">
-        <v>9.721131940903236</v>
+        <v>1.579683940396776</v>
       </c>
       <c r="F3" t="n">
-        <v>9.692963494232188</v>
+        <v>1.575106567812731</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.39163917463154</v>
+        <v>5.751141365877626</v>
       </c>
       <c r="D4" t="n">
-        <v>35.12795288261736</v>
+        <v>5.708292343425321</v>
       </c>
       <c r="E4" t="n">
-        <v>9.721131940903236</v>
+        <v>1.579683940396776</v>
       </c>
       <c r="F4" t="n">
-        <v>9.692963494232188</v>
+        <v>1.575106567812731</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.14996628774807</v>
+        <v>6.199369521759062</v>
       </c>
       <c r="D5" t="n">
-        <v>38.47488083240109</v>
+        <v>6.252168135265178</v>
       </c>
       <c r="E5" t="n">
-        <v>9.721131940903236</v>
+        <v>1.579683940396776</v>
       </c>
       <c r="F5" t="n">
-        <v>9.692963494232188</v>
+        <v>1.575106567812731</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.76625490381443</v>
+        <v>4.837016421869845</v>
       </c>
       <c r="D6" t="n">
-        <v>30.15532285250566</v>
+        <v>4.900239963532171</v>
       </c>
       <c r="E6" t="n">
-        <v>9.721131940903236</v>
+        <v>1.579683940396776</v>
       </c>
       <c r="F6" t="n">
-        <v>9.692963494232188</v>
+        <v>1.575106567812731</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.31666328022094</v>
+        <v>6.713957783035903</v>
       </c>
       <c r="D7" t="n">
-        <v>41.70907683017882</v>
+        <v>6.777724984904059</v>
       </c>
       <c r="E7" t="n">
-        <v>9.721131940903236</v>
+        <v>1.579683940396776</v>
       </c>
       <c r="F7" t="n">
-        <v>9.692963494232188</v>
+        <v>1.575106567812731</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.74136355232202</v>
+        <v>4.020471577252329</v>
       </c>
       <c r="D8" t="n">
-        <v>25.12659803548872</v>
+        <v>4.083072180766917</v>
       </c>
       <c r="E8" t="n">
-        <v>9.721131940903236</v>
+        <v>1.579683940396776</v>
       </c>
       <c r="F8" t="n">
-        <v>9.692963494232188</v>
+        <v>1.575106567812731</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.19288787585343</v>
+        <v>5.556344279826183</v>
       </c>
       <c r="D9" t="n">
-        <v>34.58513363641828</v>
+        <v>5.620084215917972</v>
       </c>
       <c r="E9" t="n">
-        <v>9.721131940903236</v>
+        <v>1.579683940396776</v>
       </c>
       <c r="F9" t="n">
-        <v>9.692963494232188</v>
+        <v>1.575106567812731</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.13498870070767</v>
+        <v>5.709435663864996</v>
       </c>
       <c r="D10" t="n">
-        <v>35.05994084286532</v>
+        <v>5.697240386965615</v>
       </c>
       <c r="E10" t="n">
-        <v>9.721131940903236</v>
+        <v>1.579683940396776</v>
       </c>
       <c r="F10" t="n">
-        <v>9.692963494232188</v>
+        <v>1.575106567812731</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
